--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/ ESTATOR COMPLETO 09_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/ ESTATOR COMPLETO 09_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,7 +457,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -792,7 +796,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -834,7 +842,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -855,7 +867,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -897,7 +913,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1106,12 +1126,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7898508611209</t>
+          <t>7898932690016</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ESTAROR BOBINA PULSO MAGNETRON CG125 FAN KS/ES 2009 A 2015 90278670</t>
+          <t>ESTATOR MAGNETO COMPLETO BHD CG TITAN FAN125 2002 A 2004</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1119,11 +1139,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1131,12 +1147,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7898485614323</t>
+          <t>7899333760018</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ESTAROR BOBINA PULSO MAGNETRON CG TITAN150 KS/ES/ESD 2004 A 2008</t>
+          <t>ESTATOR MAGNETO BHD POP110I/ TITAN125</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1144,7 +1160,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1152,45 +1172,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7898932690016</t>
+          <t>7908885006311</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ESTATOR MAGNETO COMPLETO BHD CG TITAN FAN125 2002 A 2004</t>
+          <t>ESTATOR COMPLETO RIIE FAN125 2014 001099</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>33</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>7899333760018</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ESTATOR MAGNETO BHD POP110I/ TITAN125</t>
+          <t>ESTATOR RT TORNADO250</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1198,38 +1214,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7908885006311</t>
+          <t>7895099120530</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ESTATOR COMPLETO RIIE FAN125 2014 001099</t>
+          <t>ESTATOR COMPLETO IRON GG TITAN FAN125 2009 EM DIANTE 27500</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>35</v>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>7898475500018</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ESTATOR RT TORNADO250</t>
+          <t>ESTATOR COMPLETO BHD BROS NXR150 2009 MIX/FLEX</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1240,12 +1256,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7895099120530</t>
+          <t>070341177549</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ESTATOR COMPLETO IRON GG TITAN FAN125 2009 EM DIANTE 27500</t>
+          <t>ESTATOR COMPLETO IRON BURMAN125I 2012 A 2018 350418</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1261,20 +1277,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7898475500018</t>
+          <t>7895099120493</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ESTATOR COMPLETO BHD BROS NXR150 2009 MIX/FLEX</t>
+          <t>ESTATOR COMPLETO IRON SPEED150/ KANSAS150 27496</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1282,12 +1302,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>070341177549</t>
+          <t>7895099120394</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ESTATOR COMPLETO IRON BURMAN125I 2012 A 2018 350418</t>
+          <t>ESTATOR COMPLETO IRON CG TITAN FAN125 2003 A 2008 27486</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1295,53 +1315,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>7895099120493</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>ESTATOR COMPLETO IRON SPEED150/ KANSAS150 27496</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>7895099120394</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ESTATOR COMPLETO IRON CG TITAN FAN125 2003 A 2008 27486</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>127</t>
         </is>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/ ESTATOR COMPLETO 09_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/ ESTATOR COMPLETO 09_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,7 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,7 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -524,7 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -545,7 +532,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,7 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -587,7 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -608,7 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -629,7 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -650,11 +632,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -675,11 +652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -700,11 +672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -725,11 +692,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -750,11 +712,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -775,7 +732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -796,11 +752,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -821,7 +772,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -842,11 +792,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -867,11 +812,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -892,7 +832,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -913,11 +852,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -925,7 +859,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7895099125696</t>
+          <t>220</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -938,7 +872,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,7 +892,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -980,11 +912,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1005,7 +932,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1026,7 +952,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,7 +972,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1065,12 +989,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>185</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1093,11 +1012,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1118,7 +1032,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1139,7 +1052,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1160,11 +1072,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,11 +1092,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1198,7 +1100,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ESTATOR RT TORNADO250</t>
+          <t>ESTATOR RT TORNADO 250</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1206,7 +1108,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1224,10 +1125,9 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1248,7 +1148,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1269,7 +1168,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1290,11 +1188,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1313,11 +1206,6 @@
       <c r="D40" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>127</t>
         </is>
       </c>
     </row>
